--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>136582995</v>
       </c>
       <c r="B45" t="n">
-        <v>92780</v>
+        <v>92783</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ67"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134493939</v>
+        <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>91995</v>
+        <v>93404</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5231,21 +5231,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>325361</v>
+        <v>325518</v>
       </c>
       <c r="R43" t="n">
-        <v>6556573</v>
+        <v>6556389</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,21 +5301,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5331,38 +5316,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493939</t>
+          <t>https://artportalen.se/Sighting/136707273</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134493930</v>
+        <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>91937</v>
+        <v>93404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5372,10 +5357,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>325481</v>
+        <v>325273</v>
       </c>
       <c r="R44" t="n">
-        <v>6556387</v>
+        <v>6556667</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5402,12 +5387,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,21 +5403,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5448,65 +5418,54 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493930</t>
+          <t>https://artportalen.se/Sighting/136707312</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136582995</v>
+        <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>92783</v>
+        <v>93404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>325183</v>
+        <v>325243</v>
       </c>
       <c r="R45" t="n">
-        <v>6556846</v>
+        <v>6556671</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5530,12 +5489,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5544,39 +5503,33 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136582995</t>
+          <t>https://artportalen.se/Sighting/136707314</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134245897</v>
+        <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>75468</v>
+        <v>93404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5584,37 +5537,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ravin nordväst, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>325008</v>
+        <v>325266</v>
       </c>
       <c r="R46" t="n">
-        <v>6557270</v>
+        <v>6556725</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5641,12 +5591,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5655,34 +5605,33 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134245897</t>
+          <t>https://artportalen.se/Sighting/136707315</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134246089</v>
+        <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>79992</v>
+        <v>93404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5690,40 +5639,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>325136</v>
+        <v>325277</v>
       </c>
       <c r="R47" t="n">
-        <v>6557020</v>
+        <v>6556758</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5747,12 +5693,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5761,34 +5707,33 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246089</t>
+          <t>https://artportalen.se/Sighting/136707316</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134288659</v>
+        <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>79992</v>
+        <v>93404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,44 +5741,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>325338</v>
+        <v>325228</v>
       </c>
       <c r="R48" t="n">
-        <v>6556520</v>
+        <v>6556790</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5857,12 +5795,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5871,54 +5809,33 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stubbe # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134288659</t>
+          <t>https://artportalen.se/Sighting/136707320</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134493940</v>
+        <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>79992</v>
+        <v>93404</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5926,21 +5843,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5950,10 +5867,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>325365</v>
+        <v>325103</v>
       </c>
       <c r="R49" t="n">
-        <v>6556582</v>
+        <v>6557035</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5980,12 +5897,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,21 +5913,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6026,16 +5928,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493940</t>
+          <t>https://artportalen.se/Sighting/136707326</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134493949</v>
+        <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>79992</v>
+        <v>93404</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6043,21 +5945,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6067,10 +5969,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>325128</v>
+        <v>325123</v>
       </c>
       <c r="R50" t="n">
-        <v>6557028</v>
+        <v>6557061</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6097,12 +5999,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6113,21 +6015,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6143,16 +6030,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493949</t>
+          <t>https://artportalen.se/Sighting/136707327</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136583741</v>
+        <v>134493939</v>
       </c>
       <c r="B51" t="n">
-        <v>80093</v>
+        <v>91995</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6160,44 +6047,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325124</v>
+        <v>325361</v>
       </c>
       <c r="R51" t="n">
-        <v>6557001</v>
+        <v>6556573</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6221,12 +6101,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6235,15 +6115,9 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AJ51" t="inlineStr">
         <is>
           <t>tall</t>
@@ -6256,33 +6130,33 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stubbe # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583741</t>
+          <t>https://artportalen.se/Sighting/134493939</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133657356</v>
+        <v>134493930</v>
       </c>
       <c r="B52" t="n">
-        <v>57972</v>
+        <v>91937</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6290,37 +6164,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325284</v>
+        <v>325481</v>
       </c>
       <c r="R52" t="n">
-        <v>6556743</v>
+        <v>6556387</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6344,17 +6218,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6366,35 +6235,45 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Tallskog.</t>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657356</t>
+          <t>https://artportalen.se/Sighting/134493930</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133657357</v>
+        <v>136582995</v>
       </c>
       <c r="B53" t="n">
-        <v>57972</v>
+        <v>92784</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6402,34 +6281,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325321</v>
+        <v>325183</v>
       </c>
       <c r="R53" t="n">
-        <v>6556585</v>
+        <v>6556846</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6456,17 +6346,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6475,88 +6360,80 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657357</t>
+          <t>https://artportalen.se/Sighting/136582995</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134246027</v>
+        <v>134245897</v>
       </c>
       <c r="B54" t="n">
-        <v>57972</v>
+        <v>75468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ravin nordväst, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325114</v>
+        <v>325008</v>
       </c>
       <c r="R54" t="n">
-        <v>6557125</v>
+        <v>6557270</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6594,6 +6471,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6611,52 +6489,43 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246027</t>
+          <t>https://artportalen.se/Sighting/134245897</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133696600</v>
+        <v>134246089</v>
       </c>
       <c r="B55" t="n">
-        <v>57169</v>
+        <v>79992</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6664,13 +6533,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325266</v>
+        <v>325136</v>
       </c>
       <c r="R55" t="n">
-        <v>6556841</v>
+        <v>6557020</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6694,12 +6563,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6708,6 +6577,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6725,51 +6595,58 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696600</t>
+          <t>https://artportalen.se/Sighting/134246089</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133659796</v>
+        <v>134288659</v>
       </c>
       <c r="B56" t="n">
-        <v>4776</v>
+        <v>79992</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325488</v>
+        <v>325338</v>
       </c>
       <c r="R56" t="n">
-        <v>6556147</v>
+        <v>6556520</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6796,12 +6673,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6810,90 +6687,92 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/134288659</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134246129</v>
+        <v>134493940</v>
       </c>
       <c r="B57" t="n">
-        <v>4776</v>
+        <v>79992</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325208</v>
+        <v>325365</v>
       </c>
       <c r="R57" t="n">
-        <v>6556981</v>
+        <v>6556582</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6917,12 +6796,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6931,74 +6810,83 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/134493940</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493920</v>
+        <v>134493949</v>
       </c>
       <c r="B58" t="n">
-        <v>5181</v>
+        <v>79992</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325483</v>
+        <v>325128</v>
       </c>
       <c r="R58" t="n">
-        <v>6556127</v>
+        <v>6557028</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7044,17 +6932,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7071,59 +6959,61 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/134493949</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493951</v>
+        <v>136583741</v>
       </c>
       <c r="B59" t="n">
-        <v>5181</v>
+        <v>80093</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325037</v>
+        <v>325124</v>
       </c>
       <c r="R59" t="n">
-        <v>6557099</v>
+        <v>6557001</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7147,12 +7037,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7161,48 +7051,54 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/136583741</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133696603</v>
+        <v>133657356</v>
       </c>
       <c r="B60" t="n">
-        <v>58461</v>
+        <v>57972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7210,49 +7106,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325266</v>
+        <v>325284</v>
       </c>
       <c r="R60" t="n">
-        <v>6556841</v>
+        <v>6556743</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7276,12 +7160,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7292,31 +7181,36 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/133657356</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134493919</v>
+        <v>133657357</v>
       </c>
       <c r="B61" t="n">
-        <v>5201</v>
+        <v>57972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7324,16 +7218,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7342,24 +7236,19 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325523</v>
+        <v>325321</v>
       </c>
       <c r="R61" t="n">
-        <v>6556083</v>
+        <v>6556585</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7383,12 +7272,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7400,45 +7294,35 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/133657357</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134493921</v>
+        <v>134246027</v>
       </c>
       <c r="B62" t="n">
-        <v>5201</v>
+        <v>57972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7446,16 +7330,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7463,25 +7347,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325483</v>
+        <v>325114</v>
       </c>
       <c r="R62" t="n">
-        <v>6556127</v>
+        <v>6557125</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7505,12 +7396,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7521,46 +7412,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134246027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134493929</v>
+        <v>133696600</v>
       </c>
       <c r="B63" t="n">
-        <v>5201</v>
+        <v>57169</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,42 +7444,49 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>325481</v>
+        <v>325266</v>
       </c>
       <c r="R63" t="n">
-        <v>6556387</v>
+        <v>6556841</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7627,12 +7510,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7643,46 +7526,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/133696600</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134493932</v>
+        <v>133659796</v>
       </c>
       <c r="B64" t="n">
-        <v>5201</v>
+        <v>4776</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7690,42 +7558,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>325436</v>
+        <v>325488</v>
       </c>
       <c r="R64" t="n">
-        <v>6556446</v>
+        <v>6556147</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7749,12 +7612,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7766,45 +7629,40 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134493937</v>
+        <v>134246129</v>
       </c>
       <c r="B65" t="n">
-        <v>5201</v>
+        <v>4776</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7812,42 +7670,46 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>325438</v>
+        <v>325208</v>
       </c>
       <c r="R65" t="n">
-        <v>6556553</v>
+        <v>6556981</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7871,12 +7733,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7885,48 +7747,34 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134493947</v>
+        <v>136707324</v>
       </c>
       <c r="B66" t="n">
-        <v>8460</v>
+        <v>4777</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7934,21 +7782,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7963,10 +7811,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>325197</v>
+        <v>325067</v>
       </c>
       <c r="R66" t="n">
-        <v>6556991</v>
+        <v>6557022</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7993,12 +7841,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8012,17 +7860,17 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8039,16 +7887,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
+          <t>https://artportalen.se/Sighting/136707324</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134493943</v>
+        <v>134493920</v>
       </c>
       <c r="B67" t="n">
-        <v>8449</v>
+        <v>5181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8056,21 +7904,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8085,10 +7933,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>325364</v>
+        <v>325483</v>
       </c>
       <c r="R67" t="n">
-        <v>6556631</v>
+        <v>6556127</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8132,6 +7980,21 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
@@ -8145,6 +8008,1691 @@
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493920</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134493951</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>325037</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6557099</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493951</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>133696603</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>325266</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6556841</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696603</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134493919</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>325523</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6556083</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493919</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134493921</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>325483</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6556127</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493921</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134493929</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>325481</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6556387</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493929</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134493932</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>325436</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6556446</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493932</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134493937</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>325438</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6556553</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493937</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134493947</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>325197</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6556991</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493947</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136707311</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>325374</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6556641</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707311</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136707318</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>325272</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6556773</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707318</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136707321</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>325230</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6556894</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707321</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>136707323</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>325126</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6556997</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707323</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>136707328</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>325148</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6557073</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707328</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134493943</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>325364</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6556631</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -8218,6 +9766,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>136582995</v>
       </c>
       <c r="B53" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136583741</v>
       </c>
       <c r="B59" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>136582995</v>
       </c>
       <c r="B53" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ81"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6036,10 +6036,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134493939</v>
+        <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>91995</v>
+        <v>93411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6047,21 +6047,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325361</v>
+        <v>325074</v>
       </c>
       <c r="R51" t="n">
-        <v>6556573</v>
+        <v>6557067</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6101,12 +6101,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6117,21 +6117,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6147,38 +6132,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493939</t>
+          <t>https://artportalen.se/Sighting/136890231</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134493930</v>
+        <v>134493939</v>
       </c>
       <c r="B52" t="n">
-        <v>91937</v>
+        <v>91995</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6188,10 +6173,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325481</v>
+        <v>325361</v>
       </c>
       <c r="R52" t="n">
-        <v>6556387</v>
+        <v>6556573</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6237,17 +6222,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6264,16 +6249,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493930</t>
+          <t>https://artportalen.se/Sighting/134493939</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136582995</v>
+        <v>134493930</v>
       </c>
       <c r="B53" t="n">
-        <v>92791</v>
+        <v>91937</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,48 +6266,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6031</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325183</v>
+        <v>325481</v>
       </c>
       <c r="R53" t="n">
-        <v>6556846</v>
+        <v>6556387</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6346,12 +6320,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6360,80 +6334,97 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136582995</t>
+          <t>https://artportalen.se/Sighting/134493930</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134245897</v>
+        <v>136582995</v>
       </c>
       <c r="B54" t="n">
-        <v>75468</v>
+        <v>92791</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>6031</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ravin nordväst, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325008</v>
+        <v>325183</v>
       </c>
       <c r="R54" t="n">
-        <v>6557270</v>
+        <v>6556846</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6457,12 +6448,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6475,30 +6466,35 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134245897</t>
+          <t>https://artportalen.se/Sighting/136582995</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134246089</v>
+        <v>134245897</v>
       </c>
       <c r="B55" t="n">
-        <v>79992</v>
+        <v>75468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6506,21 +6502,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6529,17 +6525,17 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ravin nordväst, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325136</v>
+        <v>325008</v>
       </c>
       <c r="R55" t="n">
-        <v>6557020</v>
+        <v>6557270</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6595,13 +6591,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246089</t>
+          <t>https://artportalen.se/Sighting/134245897</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134288659</v>
+        <v>134246089</v>
       </c>
       <c r="B56" t="n">
         <v>79992</v>
@@ -6630,11 +6626,7 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -6643,10 +6635,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325338</v>
+        <v>325136</v>
       </c>
       <c r="R56" t="n">
-        <v>6556520</v>
+        <v>6557020</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6673,12 +6665,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6691,47 +6683,27 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stubbe # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134288659</t>
+          <t>https://artportalen.se/Sighting/134246089</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134493940</v>
+        <v>134288659</v>
       </c>
       <c r="B57" t="n">
         <v>79992</v>
@@ -6760,19 +6732,26 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325365</v>
+        <v>325338</v>
       </c>
       <c r="R57" t="n">
-        <v>6556582</v>
+        <v>6556520</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6796,12 +6775,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6810,9 +6789,15 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AJ57" t="inlineStr">
         <is>
           <t>tall</t>
@@ -6825,30 +6810,30 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Stubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493940</t>
+          <t>https://artportalen.se/Sighting/134288659</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493949</v>
+        <v>134493940</v>
       </c>
       <c r="B58" t="n">
         <v>79992</v>
@@ -6883,10 +6868,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325128</v>
+        <v>325365</v>
       </c>
       <c r="R58" t="n">
-        <v>6557028</v>
+        <v>6556582</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6959,16 +6944,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493949</t>
+          <t>https://artportalen.se/Sighting/134493940</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136583741</v>
+        <v>134493949</v>
       </c>
       <c r="B59" t="n">
-        <v>80095</v>
+        <v>79992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6994,26 +6979,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325124</v>
+        <v>325128</v>
       </c>
       <c r="R59" t="n">
-        <v>6557001</v>
+        <v>6557028</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7037,12 +7015,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7051,15 +7029,9 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AJ59" t="inlineStr">
         <is>
           <t>tall</t>
@@ -7072,68 +7044,75 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stubbe # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583741</t>
+          <t>https://artportalen.se/Sighting/134493949</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133657356</v>
+        <v>136583741</v>
       </c>
       <c r="B60" t="n">
-        <v>57972</v>
+        <v>80095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325284</v>
+        <v>325124</v>
       </c>
       <c r="R60" t="n">
-        <v>6556743</v>
+        <v>6557001</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7160,17 +7139,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7179,35 +7153,51 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657356</t>
+          <t>https://artportalen.se/Sighting/136583741</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133657357</v>
+        <v>133657356</v>
       </c>
       <c r="B61" t="n">
         <v>57972</v>
@@ -7238,14 +7228,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325321</v>
+        <v>325284</v>
       </c>
       <c r="R61" t="n">
-        <v>6556585</v>
+        <v>6556743</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7313,13 +7303,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657357</t>
+          <t>https://artportalen.se/Sighting/133657356</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134246027</v>
+        <v>133657357</v>
       </c>
       <c r="B62" t="n">
         <v>57972</v>
@@ -7347,29 +7337,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325114</v>
+        <v>325321</v>
       </c>
       <c r="R62" t="n">
-        <v>6557125</v>
+        <v>6556585</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7396,12 +7374,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7412,31 +7395,36 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246027</t>
+          <t>https://artportalen.se/Sighting/133657357</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133696600</v>
+        <v>134246027</v>
       </c>
       <c r="B63" t="n">
-        <v>57169</v>
+        <v>57972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,21 +7432,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7467,12 +7455,12 @@
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7480,13 +7468,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>325266</v>
+        <v>325114</v>
       </c>
       <c r="R63" t="n">
-        <v>6556841</v>
+        <v>6557125</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7510,12 +7498,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7541,16 +7529,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696600</t>
+          <t>https://artportalen.se/Sighting/134246027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133659796</v>
+        <v>133696600</v>
       </c>
       <c r="B64" t="n">
-        <v>4776</v>
+        <v>57169</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7558,37 +7546,49 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>325488</v>
+        <v>325266</v>
       </c>
       <c r="R64" t="n">
-        <v>6556147</v>
+        <v>6556841</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7628,38 +7628,28 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/133696600</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134246129</v>
+        <v>133659796</v>
       </c>
       <c r="B65" t="n">
         <v>4776</v>
@@ -7688,25 +7678,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>325208</v>
+        <v>325488</v>
       </c>
       <c r="R65" t="n">
-        <v>6556981</v>
+        <v>6556147</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7733,12 +7714,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7747,34 +7728,43 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136707324</v>
+        <v>134246129</v>
       </c>
       <c r="B66" t="n">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7800,24 +7790,28 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>325067</v>
+        <v>325208</v>
       </c>
       <c r="R66" t="n">
-        <v>6557022</v>
+        <v>6556981</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7841,12 +7835,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7855,48 +7849,34 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707324</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134493920</v>
+        <v>136707324</v>
       </c>
       <c r="B67" t="n">
-        <v>5181</v>
+        <v>4777</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7904,21 +7884,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7933,10 +7913,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>325483</v>
+        <v>325067</v>
       </c>
       <c r="R67" t="n">
-        <v>6556127</v>
+        <v>6557022</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7963,12 +7943,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8009,13 +7989,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/136707324</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134493951</v>
+        <v>134493920</v>
       </c>
       <c r="B68" t="n">
         <v>5181</v>
@@ -8055,10 +8035,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>325037</v>
+        <v>325483</v>
       </c>
       <c r="R68" t="n">
-        <v>6557099</v>
+        <v>6556127</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8131,16 +8111,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133696603</v>
+        <v>134493951</v>
       </c>
       <c r="B69" t="n">
-        <v>58461</v>
+        <v>5181</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8148,49 +8128,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103018</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>325266</v>
+        <v>325037</v>
       </c>
       <c r="R69" t="n">
-        <v>6556841</v>
+        <v>6557099</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8214,12 +8187,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8230,31 +8203,46 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134493919</v>
+        <v>133696603</v>
       </c>
       <c r="B70" t="n">
-        <v>5201</v>
+        <v>58461</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8262,42 +8250,49 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105930</v>
+        <v>103018</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>325523</v>
+        <v>325266</v>
       </c>
       <c r="R70" t="n">
-        <v>6556083</v>
+        <v>6556841</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8321,12 +8316,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8337,43 +8332,28 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134493921</v>
+        <v>134493919</v>
       </c>
       <c r="B71" t="n">
         <v>5201</v>
@@ -8413,10 +8393,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>325483</v>
+        <v>325523</v>
       </c>
       <c r="R71" t="n">
-        <v>6556127</v>
+        <v>6556083</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8489,13 +8469,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134493929</v>
+        <v>134493921</v>
       </c>
       <c r="B72" t="n">
         <v>5201</v>
@@ -8535,10 +8515,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>325481</v>
+        <v>325483</v>
       </c>
       <c r="R72" t="n">
-        <v>6556387</v>
+        <v>6556127</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8611,13 +8591,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134493932</v>
+        <v>134493929</v>
       </c>
       <c r="B73" t="n">
         <v>5201</v>
@@ -8657,10 +8637,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>325436</v>
+        <v>325481</v>
       </c>
       <c r="R73" t="n">
-        <v>6556446</v>
+        <v>6556387</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8733,13 +8713,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/134493929</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134493937</v>
+        <v>134493932</v>
       </c>
       <c r="B74" t="n">
         <v>5201</v>
@@ -8779,10 +8759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>325438</v>
+        <v>325436</v>
       </c>
       <c r="R74" t="n">
-        <v>6556553</v>
+        <v>6556446</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8855,16 +8835,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493932</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134493947</v>
+        <v>134493937</v>
       </c>
       <c r="B75" t="n">
-        <v>8460</v>
+        <v>5201</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8872,21 +8852,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8901,10 +8881,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>325197</v>
+        <v>325438</v>
       </c>
       <c r="R75" t="n">
-        <v>6556991</v>
+        <v>6556553</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8950,17 +8930,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8977,16 +8957,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
+          <t>https://artportalen.se/Sighting/134493937</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136707311</v>
+        <v>134493947</v>
       </c>
       <c r="B76" t="n">
-        <v>8463</v>
+        <v>8460</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9023,10 +9003,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>325374</v>
+        <v>325197</v>
       </c>
       <c r="R76" t="n">
-        <v>6556641</v>
+        <v>6556991</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9053,12 +9033,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9099,13 +9079,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707311</t>
+          <t>https://artportalen.se/Sighting/134493947</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136707318</v>
+        <v>136707311</v>
       </c>
       <c r="B77" t="n">
         <v>8463</v>
@@ -9145,10 +9125,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>325272</v>
+        <v>325374</v>
       </c>
       <c r="R77" t="n">
-        <v>6556773</v>
+        <v>6556641</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9221,13 +9201,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707318</t>
+          <t>https://artportalen.se/Sighting/136707311</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136707321</v>
+        <v>136707318</v>
       </c>
       <c r="B78" t="n">
         <v>8463</v>
@@ -9267,10 +9247,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>325230</v>
+        <v>325272</v>
       </c>
       <c r="R78" t="n">
-        <v>6556894</v>
+        <v>6556773</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9343,13 +9323,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707321</t>
+          <t>https://artportalen.se/Sighting/136707318</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136707323</v>
+        <v>136707321</v>
       </c>
       <c r="B79" t="n">
         <v>8463</v>
@@ -9389,10 +9369,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>325126</v>
+        <v>325230</v>
       </c>
       <c r="R79" t="n">
-        <v>6556997</v>
+        <v>6556894</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9465,13 +9445,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707323</t>
+          <t>https://artportalen.se/Sighting/136707321</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136707328</v>
+        <v>136707323</v>
       </c>
       <c r="B80" t="n">
         <v>8463</v>
@@ -9511,10 +9491,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>325148</v>
+        <v>325126</v>
       </c>
       <c r="R80" t="n">
-        <v>6557073</v>
+        <v>6556997</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9587,16 +9567,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707328</t>
+          <t>https://artportalen.se/Sighting/136707323</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134493943</v>
+        <v>136707328</v>
       </c>
       <c r="B81" t="n">
-        <v>8449</v>
+        <v>8463</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9604,21 +9584,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9633,10 +9613,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>325364</v>
+        <v>325148</v>
       </c>
       <c r="R81" t="n">
-        <v>6556631</v>
+        <v>6557073</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9663,12 +9643,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9679,6 +9659,21 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9693,6 +9688,357 @@
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707328</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>136890269</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>325316</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6556570</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890269</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>136890270</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>325256</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6556560</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890270</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134493943</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>325364</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6556631</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -9780,6 +10126,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>136582995</v>
       </c>
       <c r="B54" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>136583741</v>
       </c>
       <c r="B60" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>136582995</v>
       </c>
       <c r="B54" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>136583741</v>
       </c>
       <c r="B60" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -7652,7 +7652,7 @@
         <v>133659796</v>
       </c>
       <c r="B65" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>134246129</v>
       </c>
       <c r="B66" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>134493920</v>
       </c>
       <c r="B68" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>134493951</v>
       </c>
       <c r="B69" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>136582995</v>
       </c>
       <c r="B54" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>136583741</v>
       </c>
       <c r="B60" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>136582995</v>
       </c>
       <c r="B54" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>136582995</v>
       </c>
       <c r="B54" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>136583741</v>
       </c>
       <c r="B60" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -3337,7 +3337,7 @@
         <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>136582995</v>
       </c>
       <c r="B54" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>136583741</v>
       </c>
       <c r="B60" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136707311</v>
       </c>
       <c r="B77" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>136707318</v>
       </c>
       <c r="B78" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>136707321</v>
       </c>
       <c r="B79" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136707323</v>
       </c>
       <c r="B80" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136707328</v>
       </c>
       <c r="B81" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>136890269</v>
       </c>
       <c r="B82" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>136890270</v>
       </c>
       <c r="B83" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -7793,11 +7793,7 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7902,11 +7898,7 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -8024,11 +8016,7 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -8146,11 +8134,7 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9114,11 +9098,7 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9236,11 +9216,7 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9358,11 +9334,7 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9480,11 +9452,7 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9602,11 +9570,7 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9724,11 +9688,7 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9846,11 +9806,7 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ84"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6372,44 +6372,36 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136582995</v>
+        <v>137281973</v>
       </c>
       <c r="B54" t="n">
-        <v>92808</v>
+        <v>92814</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6031</v>
+        <v>5454</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -6418,13 +6410,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325183</v>
+        <v>325103</v>
       </c>
       <c r="R54" t="n">
-        <v>6556846</v>
+        <v>6557029</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6448,12 +6440,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6462,80 +6454,102 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136582995</t>
+          <t>https://artportalen.se/Sighting/137281973</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134245897</v>
+        <v>136582995</v>
       </c>
       <c r="B55" t="n">
-        <v>75468</v>
+        <v>92808</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>6031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ravin nordväst, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325008</v>
+        <v>325183</v>
       </c>
       <c r="R55" t="n">
-        <v>6557270</v>
+        <v>6556846</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6559,12 +6573,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6577,30 +6591,35 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134245897</t>
+          <t>https://artportalen.se/Sighting/136582995</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134246089</v>
+        <v>134245897</v>
       </c>
       <c r="B56" t="n">
-        <v>79992</v>
+        <v>75468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6608,21 +6627,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6631,17 +6650,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ravin nordväst, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325136</v>
+        <v>325008</v>
       </c>
       <c r="R56" t="n">
-        <v>6557020</v>
+        <v>6557270</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6697,13 +6716,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246089</t>
+          <t>https://artportalen.se/Sighting/134245897</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134288659</v>
+        <v>134246089</v>
       </c>
       <c r="B57" t="n">
         <v>79992</v>
@@ -6732,11 +6751,7 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6745,10 +6760,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325338</v>
+        <v>325136</v>
       </c>
       <c r="R57" t="n">
-        <v>6556520</v>
+        <v>6557020</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6775,12 +6790,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6793,47 +6808,27 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stubbe # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134288659</t>
+          <t>https://artportalen.se/Sighting/134246089</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493940</v>
+        <v>134288659</v>
       </c>
       <c r="B58" t="n">
         <v>79992</v>
@@ -6862,19 +6857,26 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325365</v>
+        <v>325338</v>
       </c>
       <c r="R58" t="n">
-        <v>6556582</v>
+        <v>6556520</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6898,12 +6900,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6912,9 +6914,15 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AJ58" t="inlineStr">
         <is>
           <t>tall</t>
@@ -6927,30 +6935,30 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Stubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493940</t>
+          <t>https://artportalen.se/Sighting/134288659</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493949</v>
+        <v>134493940</v>
       </c>
       <c r="B59" t="n">
         <v>79992</v>
@@ -6985,10 +6993,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325128</v>
+        <v>325365</v>
       </c>
       <c r="R59" t="n">
-        <v>6557028</v>
+        <v>6556582</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7061,16 +7069,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493949</t>
+          <t>https://artportalen.se/Sighting/134493940</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136583741</v>
+        <v>134493949</v>
       </c>
       <c r="B60" t="n">
-        <v>80107</v>
+        <v>79992</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7096,26 +7104,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325124</v>
+        <v>325128</v>
       </c>
       <c r="R60" t="n">
-        <v>6557001</v>
+        <v>6557028</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7139,12 +7140,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7153,15 +7154,9 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AJ60" t="inlineStr">
         <is>
           <t>tall</t>
@@ -7174,68 +7169,75 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stubbe # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583741</t>
+          <t>https://artportalen.se/Sighting/134493949</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133657356</v>
+        <v>136583741</v>
       </c>
       <c r="B61" t="n">
-        <v>57972</v>
+        <v>80107</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325284</v>
+        <v>325124</v>
       </c>
       <c r="R61" t="n">
-        <v>6556743</v>
+        <v>6557001</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7262,17 +7264,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,35 +7278,51 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657356</t>
+          <t>https://artportalen.se/Sighting/136583741</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133657357</v>
+        <v>133657356</v>
       </c>
       <c r="B62" t="n">
         <v>57972</v>
@@ -7340,14 +7353,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325321</v>
+        <v>325284</v>
       </c>
       <c r="R62" t="n">
-        <v>6556585</v>
+        <v>6556743</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7415,13 +7428,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657357</t>
+          <t>https://artportalen.se/Sighting/133657356</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134246027</v>
+        <v>133657357</v>
       </c>
       <c r="B63" t="n">
         <v>57972</v>
@@ -7449,29 +7462,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>325114</v>
+        <v>325321</v>
       </c>
       <c r="R63" t="n">
-        <v>6557125</v>
+        <v>6556585</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7498,12 +7499,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7514,31 +7520,36 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246027</t>
+          <t>https://artportalen.se/Sighting/133657357</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133696600</v>
+        <v>134246027</v>
       </c>
       <c r="B64" t="n">
-        <v>57169</v>
+        <v>57972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7546,21 +7557,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7569,12 +7580,12 @@
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7582,13 +7593,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>325266</v>
+        <v>325114</v>
       </c>
       <c r="R64" t="n">
-        <v>6556841</v>
+        <v>6557125</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7612,12 +7623,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7643,16 +7654,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696600</t>
+          <t>https://artportalen.se/Sighting/134246027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133659796</v>
+        <v>133696600</v>
       </c>
       <c r="B65" t="n">
-        <v>4777</v>
+        <v>57169</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7660,37 +7671,49 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>325488</v>
+        <v>325266</v>
       </c>
       <c r="R65" t="n">
-        <v>6556147</v>
+        <v>6556841</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7714,12 +7737,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7730,38 +7753,28 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/133696600</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134246129</v>
+        <v>133659796</v>
       </c>
       <c r="B66" t="n">
         <v>4777</v>
@@ -7790,21 +7803,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>325208</v>
+        <v>325488</v>
       </c>
       <c r="R66" t="n">
-        <v>6556981</v>
+        <v>6556147</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7831,12 +7839,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7845,31 +7853,40 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136707324</v>
+        <v>134246129</v>
       </c>
       <c r="B67" t="n">
         <v>4777</v>
@@ -7898,20 +7915,24 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>325067</v>
+        <v>325208</v>
       </c>
       <c r="R67" t="n">
-        <v>6557022</v>
+        <v>6556981</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7935,12 +7956,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7949,48 +7970,34 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707324</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134493920</v>
+        <v>136707324</v>
       </c>
       <c r="B68" t="n">
-        <v>5182</v>
+        <v>4777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7998,21 +8005,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8023,10 +8030,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>325483</v>
+        <v>325067</v>
       </c>
       <c r="R68" t="n">
-        <v>6556127</v>
+        <v>6557022</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8053,12 +8060,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8099,13 +8106,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/136707324</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134493951</v>
+        <v>134493920</v>
       </c>
       <c r="B69" t="n">
         <v>5182</v>
@@ -8141,10 +8148,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>325037</v>
+        <v>325483</v>
       </c>
       <c r="R69" t="n">
-        <v>6557099</v>
+        <v>6556127</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8217,16 +8224,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133696603</v>
+        <v>134493951</v>
       </c>
       <c r="B70" t="n">
-        <v>58461</v>
+        <v>5182</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8234,49 +8241,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103018</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>325266</v>
+        <v>325037</v>
       </c>
       <c r="R70" t="n">
-        <v>6556841</v>
+        <v>6557099</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8300,12 +8296,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8316,31 +8312,46 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134493919</v>
+        <v>133696603</v>
       </c>
       <c r="B71" t="n">
-        <v>5201</v>
+        <v>58461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8348,42 +8359,49 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>103018</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>325523</v>
+        <v>325266</v>
       </c>
       <c r="R71" t="n">
-        <v>6556083</v>
+        <v>6556841</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8407,12 +8425,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8423,43 +8441,28 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134493921</v>
+        <v>134493919</v>
       </c>
       <c r="B72" t="n">
         <v>5201</v>
@@ -8499,10 +8502,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>325483</v>
+        <v>325523</v>
       </c>
       <c r="R72" t="n">
-        <v>6556127</v>
+        <v>6556083</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8575,13 +8578,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134493929</v>
+        <v>134493921</v>
       </c>
       <c r="B73" t="n">
         <v>5201</v>
@@ -8621,10 +8624,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>325481</v>
+        <v>325483</v>
       </c>
       <c r="R73" t="n">
-        <v>6556387</v>
+        <v>6556127</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8697,13 +8700,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134493932</v>
+        <v>134493929</v>
       </c>
       <c r="B74" t="n">
         <v>5201</v>
@@ -8743,10 +8746,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>325436</v>
+        <v>325481</v>
       </c>
       <c r="R74" t="n">
-        <v>6556446</v>
+        <v>6556387</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8819,13 +8822,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/134493929</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134493937</v>
+        <v>134493932</v>
       </c>
       <c r="B75" t="n">
         <v>5201</v>
@@ -8865,10 +8868,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>325438</v>
+        <v>325436</v>
       </c>
       <c r="R75" t="n">
-        <v>6556553</v>
+        <v>6556446</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8941,16 +8944,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493932</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134493947</v>
+        <v>134493937</v>
       </c>
       <c r="B76" t="n">
-        <v>8460</v>
+        <v>5201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8958,21 +8961,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8987,10 +8990,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>325197</v>
+        <v>325438</v>
       </c>
       <c r="R76" t="n">
-        <v>6556991</v>
+        <v>6556553</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9036,17 +9039,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9063,16 +9066,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
+          <t>https://artportalen.se/Sighting/134493937</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136707311</v>
+        <v>134493947</v>
       </c>
       <c r="B77" t="n">
-        <v>8464</v>
+        <v>8460</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9098,17 +9101,21 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>325374</v>
+        <v>325197</v>
       </c>
       <c r="R77" t="n">
-        <v>6556641</v>
+        <v>6556991</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9135,12 +9142,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9181,13 +9188,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707311</t>
+          <t>https://artportalen.se/Sighting/134493947</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136707318</v>
+        <v>136707311</v>
       </c>
       <c r="B78" t="n">
         <v>8464</v>
@@ -9223,10 +9230,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>325272</v>
+        <v>325374</v>
       </c>
       <c r="R78" t="n">
-        <v>6556773</v>
+        <v>6556641</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9299,13 +9306,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707318</t>
+          <t>https://artportalen.se/Sighting/136707311</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136707321</v>
+        <v>136707318</v>
       </c>
       <c r="B79" t="n">
         <v>8464</v>
@@ -9341,10 +9348,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>325230</v>
+        <v>325272</v>
       </c>
       <c r="R79" t="n">
-        <v>6556894</v>
+        <v>6556773</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9417,13 +9424,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707321</t>
+          <t>https://artportalen.se/Sighting/136707318</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136707323</v>
+        <v>136707321</v>
       </c>
       <c r="B80" t="n">
         <v>8464</v>
@@ -9459,10 +9466,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>325126</v>
+        <v>325230</v>
       </c>
       <c r="R80" t="n">
-        <v>6556997</v>
+        <v>6556894</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9535,13 +9542,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707323</t>
+          <t>https://artportalen.se/Sighting/136707321</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136707328</v>
+        <v>136707323</v>
       </c>
       <c r="B81" t="n">
         <v>8464</v>
@@ -9577,10 +9584,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>325148</v>
+        <v>325126</v>
       </c>
       <c r="R81" t="n">
-        <v>6557073</v>
+        <v>6556997</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9653,13 +9660,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707328</t>
+          <t>https://artportalen.se/Sighting/136707323</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136890269</v>
+        <v>136707328</v>
       </c>
       <c r="B82" t="n">
         <v>8464</v>
@@ -9695,10 +9702,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>325316</v>
+        <v>325148</v>
       </c>
       <c r="R82" t="n">
-        <v>6556570</v>
+        <v>6557073</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9725,12 +9732,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9771,13 +9778,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136890269</t>
+          <t>https://artportalen.se/Sighting/136707328</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136890270</v>
+        <v>136890269</v>
       </c>
       <c r="B83" t="n">
         <v>8464</v>
@@ -9813,10 +9820,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>325256</v>
+        <v>325316</v>
       </c>
       <c r="R83" t="n">
-        <v>6556560</v>
+        <v>6556570</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9889,16 +9896,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136890270</t>
+          <t>https://artportalen.se/Sighting/136890269</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134493943</v>
+        <v>136890270</v>
       </c>
       <c r="B84" t="n">
-        <v>8449</v>
+        <v>8464</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9906,39 +9913,35 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>325364</v>
+        <v>325256</v>
       </c>
       <c r="R84" t="n">
-        <v>6556631</v>
+        <v>6556560</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9965,12 +9968,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9981,6 +9984,21 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9995,6 +10013,113 @@
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890270</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134493943</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>325364</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6556631</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -10085,6 +10210,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -5223,7 +5223,7 @@
         <v>136707273</v>
       </c>
       <c r="B43" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>136707312</v>
       </c>
       <c r="B44" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136707314</v>
       </c>
       <c r="B45" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136707315</v>
       </c>
       <c r="B46" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>136707316</v>
       </c>
       <c r="B47" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>136707320</v>
       </c>
       <c r="B48" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>136707326</v>
       </c>
       <c r="B49" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>136707327</v>
       </c>
       <c r="B50" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>137281973</v>
       </c>
       <c r="B54" t="n">
-        <v>92814</v>
+        <v>92824</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>133659796</v>
       </c>
       <c r="B66" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>134246129</v>
       </c>
       <c r="B67" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>136707324</v>
       </c>
       <c r="B68" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>134493920</v>
       </c>
       <c r="B69" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>134493951</v>
       </c>
       <c r="B70" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>136707311</v>
       </c>
       <c r="B78" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>136707318</v>
       </c>
       <c r="B79" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>136707321</v>
       </c>
       <c r="B80" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>136707323</v>
       </c>
       <c r="B81" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>136707328</v>
       </c>
       <c r="B82" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>136890269</v>
       </c>
       <c r="B83" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>136890270</v>
       </c>
       <c r="B84" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>137281973</v>
       </c>
       <c r="B54" t="n">
-        <v>92824</v>
+        <v>92825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>137281973</v>
       </c>
       <c r="B54" t="n">
-        <v>92825</v>
+        <v>92828</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -6039,7 +6039,7 @@
         <v>136890231</v>
       </c>
       <c r="B51" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>137281973</v>
       </c>
       <c r="B54" t="n">
-        <v>92828</v>
+        <v>92830</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
